--- a/public/templates/combine_template.xlsx
+++ b/public/templates/combine_template.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:L2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -424,24 +424,18 @@
         <v>uniform_number</v>
       </c>
       <c r="H1" t="str">
-        <v>sprint_27m_trial_1</v>
+        <v>sprint_55m</v>
       </c>
       <c r="I1" t="str">
-        <v>sprint_27m_trial_2</v>
+        <v>baserun_55m</v>
       </c>
       <c r="J1" t="str">
-        <v>sprint_54m_trial_1</v>
+        <v>measured_at</v>
       </c>
       <c r="K1" t="str">
-        <v>sprint_54m_trial_2</v>
+        <v>publish_status</v>
       </c>
       <c r="L1" t="str">
-        <v>measured_at</v>
-      </c>
-      <c r="M1" t="str">
-        <v>publish_status</v>
-      </c>
-      <c r="N1" t="str">
         <v>photo_id</v>
       </c>
     </row>
@@ -474,31 +468,25 @@
         <v/>
       </c>
       <c r="J2" t="str">
-        <v/>
+        <v>2026-05-01</v>
       </c>
       <c r="K2" t="str">
-        <v/>
+        <v>비공개</v>
       </c>
       <c r="L2" t="str">
-        <v>2026-05-01</v>
-      </c>
-      <c r="M2" t="str">
-        <v>비공개</v>
-      </c>
-      <c r="N2" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C13"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -590,84 +578,62 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>sprint_27m_trial_1</v>
+        <v>sprint_55m</v>
       </c>
       <c r="B9" t="str">
         <v>Yes/blank allowed</v>
       </c>
       <c r="C9" t="str">
-        <v>55M 직선 스프린트 1차 기록</v>
+        <v>55M 직선 스프린트 기록</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>sprint_27m_trial_2</v>
+        <v>baserun_55m</v>
       </c>
       <c r="B10" t="str">
         <v>Yes/blank allowed</v>
       </c>
       <c r="C10" t="str">
-        <v>55M 직선 스프린트 2차 기록</v>
+        <v>55M 베이스러닝 기록</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>sprint_54m_trial_1</v>
+        <v>measured_at</v>
       </c>
       <c r="B11" t="str">
-        <v>Yes/blank allowed</v>
+        <v>Optional</v>
       </c>
       <c r="C11" t="str">
-        <v>55M 베이스러닝 1차 기록</v>
+        <v>측정 일자 (YYYY-MM-DD)</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>sprint_54m_trial_2</v>
+        <v>publish_status</v>
       </c>
       <c r="B12" t="str">
-        <v>Yes/blank allowed</v>
+        <v>Optional</v>
       </c>
       <c r="C12" t="str">
-        <v>55M 베이스러닝 2차 기록</v>
+        <v>공개 / 비공개</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>measured_at</v>
+        <v>photo_id</v>
       </c>
       <c r="B13" t="str">
         <v>Optional</v>
       </c>
       <c r="C13" t="str">
-        <v>측정 일자 (YYYY-MM-DD)</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>publish_status</v>
-      </c>
-      <c r="B14" t="str">
-        <v>Optional</v>
-      </c>
-      <c r="C14" t="str">
-        <v>공개 / 비공개</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>photo_id</v>
-      </c>
-      <c r="B15" t="str">
-        <v>Optional</v>
-      </c>
-      <c r="C15" t="str">
         <v>관련 사진 연결용 식별자</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C15"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C13"/>
   </ignoredErrors>
 </worksheet>
 </file>
